--- a/data-manipulation-scripts/sheets-cleanup/sheets/TAMPA LATERAL 08_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/TAMPA LATERAL 08_02.xlsx
@@ -64,7 +64,7 @@
     <t>7899101673274</t>
   </si>
   <si>
-    <t>TAMPA LATERAL VERMELHO PRPTORK FACTOR YBR125 2003 A 2004 VERMELHO</t>
+    <t>TAMPA LATERAL VERMELHO PROTORK FACTOR YBR125 2003 A 2004 VERMELHO</t>
   </si>
   <si>
     <t>7898574857389</t>
@@ -82,7 +82,7 @@
     <t>7899093613753</t>
   </si>
   <si>
-    <t>TAMPA LATERAL PRETO MELC BRS NXR150 2004 A 2008</t>
+    <t>TAMPA LATERAL PRETO MELC BROS NXR150 2004 A 2008</t>
   </si>
   <si>
     <t>7899988701497</t>
@@ -420,7 +420,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -432,7 +434,9 @@
       <c r="C5" s="2">
         <v>2.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -456,7 +460,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -468,7 +474,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -480,7 +488,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>354.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -492,7 +502,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -504,7 +516,9 @@
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -516,7 +530,9 @@
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4"/>
